--- a/infra_auto_diag/보고서_양식_GCP.xlsx
+++ b/infra_auto_diag/보고서_양식_GCP.xlsx
@@ -1,13 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="진단 결과(GCP)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. 표지" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. 진단 대상" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-1. 요약결과(그래프)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-2. 요약 진단결과" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-1. 진단 결과" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,13 +33,29 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="FF808080"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,11 +64,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
+        <fgColor rgb="FFBFBFBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCD5B5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -54,23 +86,163 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -141,6 +313,324 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>영역별 양호율</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <view3D>
+      <rotX val="15"/>
+      <rotY val="20"/>
+      <rAngAx val="1"/>
+    </view3D>
+    <floor/>
+    <sideWall/>
+    <backWall/>
+    <plotArea>
+      <bar3DChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'2-1. 요약결과(그래프)'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'2-1. 요약결과(그래프)'!$A$4:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'2-1. 요약결과(그래프)'!$B$4:$B$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <gapDepth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+        <axId val="1000"/>
+      </bar3DChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+      <serAx>
+        <axId val="1000"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </serAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>진단 결과 분포</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pie3DChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'2-1. 요약결과(그래프)'!E3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'2-1. 요약결과(그래프)'!$D$4:$D$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'2-1. 요약결과(그래프)'!$E$4:$E$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showPercent val="1"/>
+        </dLbls>
+      </pie3DChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="26"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>영역별 양호율(레이더)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <radarChart>
+        <radarStyle val="filled"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'2-1. 요약결과(그래프)'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'2-1. 요약결과(그래프)'!$A$4:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'2-1. 요약결과(그래프)'!$B$4:$B$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </radarChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4680000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4680000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4680000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,1537 +922,2731 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="B3:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>문서번호</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>XXXXX-VA-2026XXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>작성자</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>취약점진단팀</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>보안등급</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Confidential</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>ver 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>"진단대상" 취약점 진단</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>클라우드(GCP) 진단 상세결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>SK Shieldus 2024 클라우드 보안가이드 (GCP)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B13:I13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>GCP 클라우드 취약점 진단 상세결과 (52항목)</t>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ※ 진단 대상 리스트 - 클라우드(GCP) 1대</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>진단 대상</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>계정/구독</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>리전/버전</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>용도</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>클라우드(GCP) 진단 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>진단 영역</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>양호율</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>건수</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>1. 계정 관리</t>
+        </is>
+      </c>
+      <c r="B4" s="13">
+        <f>'2-2. 요약 진단결과'!I6</f>
+        <v/>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="E4" s="12">
+        <f>COUNTIF('2-2. 요약 진단결과'!$F$6:$F$57,"양호")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>2. 권한 관리</t>
+        </is>
+      </c>
+      <c r="B5" s="13">
+        <f>'2-2. 요약 진단결과'!I7</f>
+        <v/>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>취약</t>
+        </is>
+      </c>
+      <c r="E5" s="12">
+        <f>COUNTIF('2-2. 요약 진단결과'!$F$6:$F$57,"취약")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>3. 가상 리소스 관리</t>
+        </is>
+      </c>
+      <c r="B6" s="13">
+        <f>'2-2. 요약 진단결과'!I8</f>
+        <v/>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>인터뷰 필요</t>
+        </is>
+      </c>
+      <c r="E6" s="12">
+        <f>COUNTIF('2-2. 요약 진단결과'!$F$6:$F$57,"인터뷰 필요")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>4. 운영 관리</t>
+        </is>
+      </c>
+      <c r="B7" s="13">
+        <f>'2-2. 요약 진단결과'!I9</f>
+        <v/>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="12">
+        <f>COUNTIF('2-2. 요약 진단결과'!$F$6:$F$57,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>클라우드(GCP) 취약점 진단 요약결과(52항목)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>진단항목</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>항목코드</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>세부 진단항목</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>중요도</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>진단결과</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>진단 영역</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>양호율</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>1. 계정 관리</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>사용자 계정 관리</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F6" s="2">
+        <f>'3-1. 진단 결과'!F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>1. 계정 관리</t>
+        </is>
+      </c>
+      <c r="I6" s="13">
+        <f>IFERROR(COUNTIF(F6:F17,"양호")/(COUNTA(F6:F17)-COUNTIF(F6:F17,"N/A")-COUNTIF(F6:F17,"인터뷰 필요")),1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Cloud ID 계정 정책 관리</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F7" s="2">
+        <f>'3-1. 진단 결과'!F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>2. 권한 관리</t>
+        </is>
+      </c>
+      <c r="I7" s="13">
+        <f>IFERROR(COUNTIF(F18:F20,"양호")/(COUNTA(F18:F20)-COUNTIF(F18:F20,"N/A")-COUNTIF(F18:F20,"인터뷰 필요")),1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Cloud ID 계정 패스워드 정책 관리</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F8" s="2">
+        <f>'3-1. 진단 결과'!F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>3. 가상 리소스 관리</t>
+        </is>
+      </c>
+      <c r="I8" s="13">
+        <f>IFERROR(COUNTIF(F21:F33,"양호")/(COUNTA(F21:F33)-COUNTIF(F21:F33,"N/A")-COUNTIF(F21:F33,"인터뷰 필요")),1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Identity Platform 사용자 관리</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F9" s="2">
+        <f>'3-1. 진단 결과'!F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>4. 운영 관리</t>
+        </is>
+      </c>
+      <c r="I9" s="13">
+        <f>IFERROR(COUNTIF(F34:F57,"양호")/(COUNTA(F34:F57)-COUNTIF(F34:F57,"N/A")-COUNTIF(F34:F57,"인터뷰 필요")),1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>API 활성화 및 사용 주기 관리</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F10" s="2">
+        <f>'3-1. 진단 결과'!F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>SSH 키 사용 관리</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F11" s="2">
+        <f>'3-1. 진단 결과'!F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>메타데이터 관리</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F12" s="2">
+        <f>'3-1. 진단 결과'!F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>SQL 계정 관리</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F13" s="2">
+        <f>'3-1. 진단 결과'!F13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>MFA (Multi-Factor Authentication) 설정</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F14" s="2">
+        <f>'3-1. 진단 결과'!F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>GKE 사용자 관리</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F15" s="2">
+        <f>'3-1. 진단 결과'!F15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>GKE 서비스 어카운트 관리</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F16" s="2">
+        <f>'3-1. 진단 결과'!F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>GKE 불필요한 익명 접근 관리</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F17" s="2">
+        <f>'3-1. 진단 결과'!F17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>2. 권한 관리</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>인스턴스 서비스 정책 관리</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F18" s="2">
+        <f>'3-1. 진단 결과'!F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>네트워크 서비스 정책 관리</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F19" s="2">
+        <f>'3-1. 진단 결과'!F19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>기타 서비스 정책 관리</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F20" s="2">
+        <f>'3-1. 진단 결과'!F20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>3. 가상 리소스 관리</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>ID 및 API 액세스</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F21" s="2">
+        <f>'3-1. 진단 결과'!F21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>VM 인스턴스 관리 및 보안</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="F22" s="2">
+        <f>'3-1. 진단 결과'!F22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>애플리케이션 방화벽</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F23" s="2">
+        <f>'3-1. 진단 결과'!F23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>네트워크 방화벽 인/아웃바운드 ANY 설정 관리</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F24" s="2">
+        <f>'3-1. 진단 결과'!F24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>네트워크 방화벽 인/아웃바운드 불필요 정책 관리</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F25" s="2">
+        <f>'3-1. 진단 결과'!F25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>VPC 네트워크 서브넷 관리</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F26" s="2">
+        <f>'3-1. 진단 결과'!F26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>VPC 네트워크 서브넷 비공개 구글 액세스 설정</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F27" s="2">
+        <f>'3-1. 진단 결과'!F27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>공유 VPC 관리</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F28" s="2">
+        <f>'3-1. 진단 결과'!F28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="16" t="n"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>VPN 연결 관리</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F29" s="2">
+        <f>'3-1. 진단 결과'!F29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Storage 버킷 ACL 관리</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F30" s="2">
+        <f>'3-1. 진단 결과'!F30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Storage 제어 관리</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F31" s="2">
+        <f>'3-1. 진단 결과'!F31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Storage 리소스 퍼블릭 Access 관리</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F32" s="2">
+        <f>'3-1. 진단 결과'!F32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>GKE Pod 보안 정책 관리</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F33" s="2">
+        <f>'3-1. 진단 결과'!F33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>4. 운영 관리</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>Compute Engine 디스크 암호화 설정</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F34" s="2">
+        <f>'3-1. 진단 결과'!F34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="16" t="n"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>Compute Engine 이미지 암호화 설정</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F35" s="2">
+        <f>'3-1. 진단 결과'!F35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="16" t="n"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>SQL 암호화 설정</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F36" s="2">
+        <f>'3-1. 진단 결과'!F36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="16" t="n"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>Storage 암호화 설정</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F37" s="2">
+        <f>'3-1. 진단 결과'!F37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="16" t="n"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>Storage 데이터 보안 관리</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F38" s="2">
+        <f>'3-1. 진단 결과'!F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="16" t="n"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>SQL SSL 정책 관리</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F39" s="2">
+        <f>'3-1. 진단 결과'!F39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="16" t="n"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>Load Balancing SSL 정책 관리</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F40" s="2">
+        <f>'3-1. 진단 결과'!F40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="16" t="n"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>App Engine SSL 정책 관리</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F41" s="2">
+        <f>'3-1. 진단 결과'!F41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>통신 구간 암호화 설정</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F42" s="2">
+        <f>'3-1. 진단 결과'!F42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="16" t="n"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>감사 로그 기록 및 관리</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F43" s="2">
+        <f>'3-1. 진단 결과'!F43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="16" t="n"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>감사 로그 면제 사용자 존재 여부</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F44" s="2">
+        <f>'3-1. 진단 결과'!F44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="16" t="n"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>VPC 네트워크 흐름 로그 설정 관리</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F45" s="2">
+        <f>'3-1. 진단 결과'!F45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="16" t="n"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>방화벽 로그 관리</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F46" s="2">
+        <f>'3-1. 진단 결과'!F46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="16" t="n"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>로그 보관 설정</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F47" s="2">
+        <f>'3-1. 진단 결과'!F47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="16" t="n"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>Google 계정 사용자 이상징후 알림 설정</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F48" s="2">
+        <f>'3-1. 진단 결과'!F48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="16" t="n"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>Cloud ID 계정 사용자 이상징후 알림 설정</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="F49" s="2">
+        <f>'3-1. 진단 결과'!F49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="16" t="n"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>가상 리소스 이상징후 알림 설정</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F50" s="2">
+        <f>'3-1. 진단 결과'!F50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="16" t="n"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>백업 사용 여부</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F51" s="2">
+        <f>'3-1. 진단 결과'!F51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="16" t="n"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>보안 GKE 노드 설정</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F52" s="2">
+        <f>'3-1. 진단 결과'!F52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="16" t="n"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>애플리케이션 레이어 보안 비밀 암호화 설정</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F53" s="2">
+        <f>'3-1. 진단 결과'!F53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="16" t="n"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>워크로드 아이덴티티 설정</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F54" s="2">
+        <f>'3-1. 진단 결과'!F54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="16" t="n"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>워크로드 취약점 스캔 설정</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F55" s="2">
+        <f>'3-1. 진단 결과'!F55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="16" t="n"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>GKE Cluster 로깅 설정</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F56" s="2">
+        <f>'3-1. 진단 결과'!F56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="17" t="n"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>GKE Cluster 모니터링 설정</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F57" s="2">
+        <f>'3-1. 진단 결과'!F57</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B6:B17"/>
+    <mergeCell ref="B21:B33"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B34:B57"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F6:F57">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"취약"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>ISNUMBER(SEARCH("인터뷰",F6))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>클라우드(GCP) 취약점 진단 상세결과(52항목)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>진단항목</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>항목코드</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>세부 진단항목</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>진단기준</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>진단 경로(증적 위치)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>진단결과</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>상세 내용 / 코멘트</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>관련 리소스</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>담당자</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>상세 내용 / 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>1. 계정 관리</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>사용자 계정 관리</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>양호 - 관리자 권한을 보유한 다수 계정이 존재하지 않고 불필요한 계정이 존재하지 않을 경우\n취약 - 관리자 권한을 보유한 다수 계정과 불필요한 계정이 존재하는 경우</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1. 계정 관리</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="15" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>Cloud ID 계정 정책 관리</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>양호 - Cloud ID 사용자 정보(연락처 및 직원 정보 등)가 설정되어 있을 경우\n취약 - Cloud ID 사용자 정보(연락처 및 직원 정보 등)가 설정되어 있지 않을 경우</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1. 계정 관리</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="15" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>Cloud ID 계정 패스워드 정책 관리</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>양호 - Cloud ID 계정의 패스워드 복잡성 기준 준수 및 암호 만료/재사용 제한 설정이 존재하는 경우\n취약 - Cloud ID 계정의 패스워드 복잡성 기준 준수 및 암호 만료/재사용 제한 설정이 존재하지 않는 경우</t>
         </is>
       </c>
-      <c r="H6" s="3" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1. 계정 관리</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="15" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Identity Platform 사용자 관리</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>양호 - 공급업체 설정 중 ‘익명(Anonymous)’ 인증이 존재하지 않을 경우\n취약 - 공급업체 설정 중 ‘익명(Anonymous)’ 인증이 존재하는 경우</t>
         </is>
       </c>
-      <c r="H7" s="3" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1. 계정 관리</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="15" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>API 활성화 및 사용 주기 관리</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>양호 - API 키를 사용하게 될 경우 사용 주기가 60일 이내일 경우\n취약 - API 키를 사용하게 될 경우 사용 주기가 60일 초과일 경우</t>
         </is>
       </c>
-      <c r="H8" s="3" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1. 계정 관리</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="15" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>SSH 키 사용 관리</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>양호 - SSH 키를 통해 VM 인스턴스에 접근이 가능할 경우\n취약 - SSH 키를 통하지 않고 일반 패스워드를 통해 VM 인스턴스에 접근이 가능할 경우</t>
         </is>
       </c>
-      <c r="H9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1. 계정 관리</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="15" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>메타데이터 관리</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>양호 - SSH 접근 후 메타데이터 접근 시 주요정보가 출력되거나 확인되고 있지 않을 경우\n취약 - SSH 접근 후 메타데이터 접근 시 주요정보가 출력되거나 확인되고 있을 경우</t>
         </is>
       </c>
-      <c r="H10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1. 계정 관리</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="15" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>SQL 계정 관리</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>양호 - 패스워드 활성 및 복잡도 설정이 존재하는 경우\n취약 - 패스워드 비활성 및 복잡도 설정이 존재하지 않는 경우</t>
         </is>
       </c>
-      <c r="H11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1. 계정 관리</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="15" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>MFA (Multi-Factor Authentication) 설정</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>양호 - Cloud ID 모든 사용자 계정에 MFA가 활성화되어 있을 경우\n취약 - Cloud ID 모든 사용자 계정에 MFA가 비활성화되어 있을 경우</t>
         </is>
       </c>
-      <c r="H12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1. 계정 관리</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>GKE 사용자 관리</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>양호 - GKE 리소스 접근을 위한 RBAC 설정이 인가된 사용자만 설정되어 있는 경우\n취약 - GKE 리소스 접근을 위한 RBAC 설정이 인가된 사용자만 설정되어 있지 않은 경우</t>
         </is>
       </c>
-      <c r="H13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1. 계정 관리</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="15" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>GKE 서비스 어카운트 관리</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>양호 - 네임스페이스 또는 서비스 어카운트 설정 내 automountServiceAccountToken 값이 False 로 설정된 경우\n취약 - 네임스페이스 또는 서비스 어카운트 설정 내 automountServiceAccountToken 값이 True로 설정된 경우</t>
         </is>
       </c>
-      <c r="H14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1. 계정 관리</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="15" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>GKE 불필요한 익명 접근 관리</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>양호 - ClusterRole에 system:anonymous | unauthenticated 그룹이 바인딩 되어있지 않는 경우\n취약 - ClusterRole에 system:anonymous | unauthenticated 그룹이 바인딩 되어 있는 경우</t>
         </is>
       </c>
-      <c r="H15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="15" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>2. 권한 관리</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>인스턴스 서비스 정책 관리</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>양호 - 인스턴스 서비스 IAM 사용 권한이 각각 서비스 역할에 맞게 설정되어 있을 경우\n취약 - 인스턴스 서비스 IAM 사용 권한이 각각 서비스 역할에 맞지 설정되어 있지 않을 경우</t>
         </is>
       </c>
-      <c r="H16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2. 권한 관리</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="15" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>네트워크 서비스 정책 관리</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>양호 - 네트워크 서비스 IAM 사용 권한이 각각 서비스 역할에 맞게 설정되어 있을 경우\n취약 - 네트워크 서비스 IAM 사용 권한이 각각 서비스 역할에 맞게 설정되어 있지 않을 경우</t>
         </is>
       </c>
-      <c r="H17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2. 권한 관리</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>기타 서비스 정책 관리</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>양호 - 기타 서비스 IAM 사용 권한이 각각 서비스 역할에 맞게 설정되어 있을 경우\n취약 - 기타 서비스 IAM 사용 권한이 각각 서비스 역할에 맞게 설정되어 있지 않을 경우</t>
         </is>
       </c>
-      <c r="H18" s="3" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>3. 가상 리소스 관리</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>ID 및 API 액세스</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>양호 - 서비스 역할에 맞게 API 액세스 설정이 되어 있는 경우\n취약 - 서비스 역할에 맞게 API 액세스 설정이 되어 있지 않은 경우</t>
         </is>
       </c>
-      <c r="H19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3. 가상 리소스 관리</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="15" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>VM 인스턴스 관리 및 보안</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>양호 - 인스턴스 보안 부팅 설정을 사용하고 있을 경우\n취약 - 인스턴스 보안 부팅 설정을 사용하고 있지 않을 경우</t>
         </is>
       </c>
-      <c r="H20" s="3" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>3. 가상 리소스 관리</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="15" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>애플리케이션 방화벽</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>양호 - IP 범위가 모두 허용(*) 설정이 되어 있지 않는 경우\n취약 - IP 범위가 모두 허용(*) 설정이 되어 있는 경우</t>
         </is>
       </c>
-      <c r="H21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>3. 가상 리소스 관리</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="15" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>네트워크 방화벽 인/아웃바운드 ANY 설정 관리</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>양호 - 방화벽 내 인/아웃바운드의 포트가 Any 로 허용되어 있지 않을 경우\n취약 - 방화벽 내 인/아웃바운드의 포트가 Any 로 허용되어 있을 경우</t>
         </is>
       </c>
-      <c r="H22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>3. 가상 리소스 관리</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="15" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>네트워크 방화벽 인/아웃바운드 불필요 정책 관리</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>양호 - 방화벽 내 인/아웃바운드 규칙 내 불필요한 정책(Source, Destination) 이 존재하지 않는 경우\n취약 - 방화벽 내 인/아웃바운드 규칙 내 불필요한 정책(Source, Destination)이 존재하는 경우</t>
         </is>
       </c>
-      <c r="H23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>3. 가상 리소스 관리</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="15" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>VPC 네트워크 서브넷 관리</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>양호 - 퍼블릭/프라이빗 서브넷을 단일 가상 네트워크 리소스 내 혼용하여 사용하지 않을 경우\n취약 - 퍼블릭/프라이빗 서브넷을 단일 가상 네트워크 리소스 내 혼용하여 사용하고 있을 경우</t>
         </is>
       </c>
-      <c r="H24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>3. 가상 리소스 관리</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>VPC 네트워크 서브넷 비공개 구글 액세스 설정</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>양호 - 비공개 구글 액세스를 사용하지 않는 경우\n취약 - 비공개 구글 액세스를 사용하는 경우</t>
         </is>
       </c>
-      <c r="H25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>3. 가상 리소스 관리</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="15" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>공유 VPC 관리</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>양호 - 사용 목적에 맞게 호스트 프로젝트와 서비스 프로젝트 서브넷이 공유되고 있을 경우\n취약 - 사용 목적 없이 호스트 프로젝트와 서비스 프로젝트 서브넷이 공유되고 있을 경우</t>
         </is>
       </c>
-      <c r="H26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>3. 가상 리소스 관리</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="15" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="16" t="n"/>
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D29" s="15" t="inlineStr">
         <is>
           <t>VPN 연결 관리</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
         <is>
           <t>양호 - On-Demend(프라이빗 Cloud)와 퍼블릭 Cloud 환경 간에 Cloud VPN 터널 및 게이트웨이를 연결하고 있지 않을 경우\n취약 - On-Demend(프라이빗 Cloud)와 퍼블릭 Cloud 환경 간에 Cloud VPN 터널 및 게이트웨이를 연결하고 있을 경우</t>
         </is>
       </c>
-      <c r="H27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>3. 가상 리소스 관리</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="15" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>Storage 버킷 ACL 관리</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>양호 - Storage 버킷 서비스의 ACL 계정 사용 권한이 역할에 맞게 설정되어 있을 경우\n취약 - Storage 버킷 서비스의 ACL 계정 사용 권한이 역할에 맞게 설정되어 있지 않을 경우</t>
         </is>
       </c>
-      <c r="H28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>3. 가상 리소스 관리</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="15" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>Storage 제어 관리</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>양호 - 서명된 URL을 사용하지 않거나 사용시간을 최소한으로 설정되어 있을 경우\n취약 - 서명된 URL 사용 시 사용시간을 최소한으로 설정하지 않은 경우</t>
         </is>
       </c>
-      <c r="H29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>3. 가상 리소스 관리</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="15" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>Storage 리소스 퍼블릭 Access 관리</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>양호 - Storage 버킷 내 불필요한 공개 액세스 설정이 되어 있지 않은 경우\n취약 - Storage 버킷 내 불필요한 공개 액세스 설정이 되어 있는 경우</t>
         </is>
       </c>
-      <c r="H30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>3. 가상 리소스 관리</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="15" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>3.13</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>GKE Pod 보안 정책 관리</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>양호 - PSS Profile Baseline 및 PSA Audit 이상 설정을 적용해 사용하는 경우\n취약 - PSS 및 PSA 설정을 적용하여 사용하지 않거나 PSS Profile Privileged 및 PSA warn 설정을 적용해 사용하는 경우</t>
         </is>
       </c>
-      <c r="H31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="15" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>4. 운영 관리</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>Compute Engine 디스크 암호화 설정</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>양호 - “고객 관리 키” 사용 시 키에 대한 순환 주기 설정이 되어 있을 경우\n취약 - “고객 관리 키” 사용 시 키에 대한 순환 주기 설정이 되어있지 않을 경우</t>
         </is>
       </c>
-      <c r="H32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="15" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="16" t="n"/>
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>Compute Engine 이미지 암호화 설정</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E35" s="15" t="inlineStr">
         <is>
           <t>양호 - “고객 관리 키” 사용 시 키에 대한 순환 주기 설정이 되어 있을 경우\n취약 - “고객 관리 키” 사용 시 키에 대한 순환 주기 설정이 되어있지 않을 경우</t>
         </is>
       </c>
-      <c r="H33" s="3" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="15" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="16" t="n"/>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>SQL 암호화 설정</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>양호 - “고객 관리 키” 사용 시 키에 대한 순환 주기 설정이 되어 있을 경우\n취약 - “고객 관리 키” 사용 시 키에 대한 순환 주기 설정이 되어있지 않을 경우</t>
         </is>
       </c>
-      <c r="H34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="15" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="16" t="n"/>
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>Storage 암호화 설정</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E37" s="15" t="inlineStr">
         <is>
           <t>양호 - “고객 관리 키” 사용 시 키에 대한 순환 주기 설정이 되어 있을 경우\n취약 - “고객 관리 키” 사용 시 키에 대한 순환 주기 설정이 되어있지 않을 경우</t>
         </is>
       </c>
-      <c r="H35" s="3" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="15" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="16" t="n"/>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>Storage 데이터 보안 관리</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>양호 - 장기간 보관해야 하는 객체(데이터)에 보존 정책이 설정되어 있는 경우\n취약 - 장기간 보관해야 하는 객체(데이터)에 보존 정책이 설정되어 있지 않은 경우</t>
         </is>
       </c>
-      <c r="H36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="15" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="16" t="n"/>
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D39" s="15" t="inlineStr">
         <is>
           <t>SQL SSL 정책 관리</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E39" s="15" t="inlineStr">
         <is>
           <t>양호 - 통신구간 암호화가 필요한 서비스 내 SSL 연결 설정이 존재하는 경우\n취약 - 통신구간 암호화가 필요한 서비스 내 SSL 연결 설정이 존재하지 않는 경우</t>
         </is>
       </c>
-      <c r="H37" s="3" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="15" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="16" t="n"/>
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>Load Balancing SSL 정책 관리</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>양호 - 통신구간 암호화가 필요한 대상에 SSL 연결 설정이 존재하는 경우\n취약 - 통신구간 암호화가 필요한 대상에 SSL 연결 설정이 존재하지 않는 경우</t>
         </is>
       </c>
-      <c r="H38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="15" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="16" t="n"/>
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D41" s="15" t="inlineStr">
         <is>
           <t>App Engine SSL 정책 관리</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E41" s="15" t="inlineStr">
         <is>
           <t>양호 - App Engine을 사용할 때 SSL(TLS)의 설정이 적용되어 있을 경우\n취약 - App Engine을 사용할 때 SSL(TLS)의 설정이 적용되어 있지 않을 경우</t>
         </is>
       </c>
-      <c r="H39" s="3" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="15" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>통신 구간 암호화 설정</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>양호 - 클라우드 리소스 통신 구간 내 암호화 설정이 되어 있는 경우\n취약 - 클라우드 리소스 통신 구간 내 암호화 설정이 되어 있지 않는 경우</t>
         </is>
       </c>
-      <c r="H40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="15" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="16" t="n"/>
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>4.10</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>감사 로그 기록 및 관리</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
         <is>
           <t>양호 - 서비스 별 감사 로그가 설정되어 있을 경우\n취약 - 서비스 별 감사 로그가 설정되어 있지 않을 경우</t>
         </is>
       </c>
-      <c r="H41" s="3" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="15" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="16" t="n"/>
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>4.11</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>감사 로그 면제 사용자 존재 여부</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr">
         <is>
           <t>양호 - 감사 로그 내 면제 사용자가 존재하지 않는 경우\n취약 - 감사 로그 내 면제 사용자가 존재하는 경우</t>
         </is>
       </c>
-      <c r="H42" s="3" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="15" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="16" t="n"/>
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>4.12</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>VPC 네트워크 흐름 로그 설정 관리</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E45" s="15" t="inlineStr">
         <is>
           <t>양호 - VPC 네트워크 흐름 로그 설정이 활성화 되어있는 경우\n취약 - VPC 네트워크 흐름 로그 설정이 활성화 되어있지 않은 경우</t>
         </is>
       </c>
-      <c r="H43" s="3" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="15" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="16" t="n"/>
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>4.13</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>방화벽 로그 관리</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
         <is>
           <t>양호 - Well-Known 정책에 대한 로그 설정이 존재하는 경우\n취약 - Well-Known 정책에 대한 로그 설정이 존재하지 않는 경우</t>
         </is>
       </c>
-      <c r="H44" s="3" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="15" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="16" t="n"/>
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>4.14</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>로그 보관 설정</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E47" s="15" t="inlineStr">
         <is>
           <t>양호 - GCP 서비스 로그를 기준(최소 1년 이상)에 맞게 보관하고 있는 경우\n취약 - GCP 서비스 로그를 기준(최소 1년 이상)에 맞게 보관하고 있지 않는 경우</t>
         </is>
       </c>
-      <c r="H45" s="3" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="15" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="16" t="n"/>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>4.15</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>Google 계정 사용자 이상징후 알림 설정</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>양호 - Google 계정 사용자 이상징후에 대한 알림 설정이 되어 있을 경우\n취약 - Google 계정 사용자 이상징후에 대한 알림 설정이 되어있지 않을 경우</t>
         </is>
       </c>
-      <c r="H46" s="3" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="15" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="16" t="n"/>
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>4.16</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D49" s="15" t="inlineStr">
         <is>
           <t>Cloud ID 계정 사용자 이상징후 알림 설정</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E49" s="15" t="inlineStr">
         <is>
           <t>양호 - Google 계정 사용자 이상징후에 대한 알림 설정이 되어 있을 경우\n취약 - Google 계정 사용자 이상징후에 대한 알림 설정이 되어 있지 않을 경우</t>
         </is>
       </c>
-      <c r="H47" s="3" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="15" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="16" t="n"/>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>4.17</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>가상 리소스 이상징후 알림 설정</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E50" s="15" t="inlineStr">
         <is>
           <t>양호 - 사용중인 GCP 리소스에 대한 경보가 설정되어 있을 경우\n취약 - 사용중인 GCP 리소스에 대한 경보가 설정되어 있지 않을 경우</t>
         </is>
       </c>
-      <c r="H48" s="3" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="15" t="n"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="16" t="n"/>
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>4.18</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D51" s="15" t="inlineStr">
         <is>
           <t>백업 사용 여부</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E51" s="15" t="inlineStr">
         <is>
           <t>양호 - 클라우드 리소스 백업 정책이 존재하는 경우\n취약 - 클라우드 리소스 백업 정책이 존재하지 않는 경우</t>
         </is>
       </c>
-      <c r="H49" s="3" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="15" t="n"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="16" t="n"/>
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>4.19</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>보안 GKE 노드 설정</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr">
         <is>
           <t>양호 - 보안 GKE 노드 설정이 적용 되어있는 경우\n취약 - 보안 GKE 노드 설정이 적용 되어있지 않은 경우</t>
         </is>
       </c>
-      <c r="H50" s="3" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="15" t="n"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="16" t="n"/>
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>4.20</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D53" s="15" t="inlineStr">
         <is>
           <t>애플리케이션 레이어 보안 비밀 암호화 설정</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E53" s="15" t="inlineStr">
         <is>
           <t>양호 - 애플리케이션 레이어 보안 비밀 암호화 설정이 적용 되어있는 경우\n취약 - 애플리케이션 레이어 보안 비밀 암호화 설정이 적용 되어있지 않은 경우</t>
         </is>
       </c>
-      <c r="H51" s="3" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="15" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="16" t="n"/>
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>4.21</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D54" s="15" t="inlineStr">
         <is>
           <t>워크로드 아이덴티티 설정</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr">
         <is>
           <t>양호 - Cluster 내 워크로드 아이덴티티 설정이 적용된 경우\n취약 - Cluster 내 워크로드 아이덴티티 설정이 적용되지 않은 경우</t>
         </is>
       </c>
-      <c r="H52" s="3" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="15" t="n"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="16" t="n"/>
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>4.22</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D55" s="15" t="inlineStr">
         <is>
           <t>워크로드 취약점 스캔 설정</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E55" s="15" t="inlineStr">
         <is>
           <t>양호 - Cluster 내 워크로드 취약점 스캔 설정이 적용된 경우\n취약 - Cluster 내 워크로드 취약점 스캔 설정이 적용되지 않은 경우</t>
         </is>
       </c>
-      <c r="H53" s="3" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="15" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="16" t="n"/>
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D56" s="15" t="inlineStr">
         <is>
           <t>GKE Cluster 로깅 설정</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E56" s="15" t="inlineStr">
         <is>
           <t>양호 - GKE Cluster 로깅을 설정하여 유형 별 로그를 기록하고 있는 경우\n취약 - GKE Cluster의 유형 별 로그를 기록하고 있지 않는 경우</t>
         </is>
       </c>
-      <c r="H54" s="3" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>4. 운영 관리</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="15" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="17" t="n"/>
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>4.24</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D57" s="15" t="inlineStr">
         <is>
           <t>GKE Cluster 모니터링 설정</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E57" s="15" t="inlineStr">
         <is>
           <t>양호 - GKE Cluster 모니터링에서 유형 별 알림을 설정하고 있는 경우\n취약 - GKE Cluster 모니터링 알림을 유형 별로 설정하지 않은 경우</t>
         </is>
       </c>
-      <c r="H55" s="3" t="n"/>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="15" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B6:B17"/>
+    <mergeCell ref="B21:B33"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B34:B57"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F6:F57">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"취약"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>ISNUMBER(SEARCH("인터뷰",F6))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>